--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED26.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED26.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>157W</t>
+          <t>203W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L4"/>
+  <dimension ref="B2:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-3-0068</t>
+          <t>SIM_XA_FIXED-2-0032</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,11 +1714,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>87W</t>
+          <t>147W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>第3年</t>
+          <t>第2年</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0季</t>
+          <t>4季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1748,7 +1748,62 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第3年3季</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SIM_XA_FIXED-4-0022</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>本地</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>42W</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>已交</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>第4年</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4季</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4季</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>第4年4季</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G49"/>
+  <dimension ref="B2:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2086,10 +2141,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E14" t="n">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2153,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2170,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2141,7 +2196,7 @@
         <v>-14</v>
       </c>
       <c r="E16" t="n">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,7 +2222,7 @@
         <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2193,7 +2248,7 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2219,7 +2274,7 @@
         <v>-15</v>
       </c>
       <c r="E19" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2271,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2290,14 +2345,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-8</v>
+        <v>-48</v>
       </c>
       <c r="E22" t="n">
-        <v>405</v>
+        <v>361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2306,7 +2361,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2316,14 +2371,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-14</v>
+        <v>-32</v>
       </c>
       <c r="E23" t="n">
-        <v>391</v>
+        <v>329</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2332,7 +2387,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-3357831e3d", "line_id": "L-39c61f25c8", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2342,23 +2397,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E24" t="n">
-        <v>377</v>
+        <v>317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2375,11 +2430,11 @@
         <v>-14</v>
       </c>
       <c r="E25" t="n">
-        <v>363</v>
+        <v>303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2394,23 +2449,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-36</v>
+        <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>327</v>
+        <v>289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2420,23 +2475,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-7826c7223c", "line_id": "L-39c61f25c8", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-2-0032", "receivable_term_quarters": 4, "revenue_wan": 147.0}</t>
         </is>
       </c>
     </row>
@@ -2446,23 +2501,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-14</v>
+        <v>-48</v>
       </c>
       <c r="E28" t="n">
-        <v>289</v>
+        <v>241</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2472,23 +2527,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-15</v>
+        <v>-32</v>
       </c>
       <c r="E29" t="n">
-        <v>274</v>
+        <v>209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-39c61f25c8"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-48e51883e7", "line_id": "L-39c61f25c8", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2498,23 +2553,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E30" t="n">
-        <v>274</v>
+        <v>195</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-39c61f25c8", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2524,14 +2579,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>274</v>
+        <v>181</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2540,7 +2595,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-39c61f25c8", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2550,23 +2605,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="E32" t="n">
-        <v>266</v>
+        <v>166</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>maintenance_expense | {"line_id": "L-39c61f25c8"}</t>
         </is>
       </c>
     </row>
@@ -2576,23 +2631,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>252</v>
+        <v>166</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-39c61f25c8", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2602,23 +2657,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>339</v>
+        <v>166</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 60.0, "order_id": "SIM_XA_FIXED-3-0068", "receivable_term_quarters": 0, "revenue_wan": 87.0}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-39c61f25c8", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2628,23 +2683,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-36</v>
+        <v>-12</v>
       </c>
       <c r="E35" t="n">
-        <v>303</v>
+        <v>154</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2654,23 +2709,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-24</v>
+        <v>-14</v>
       </c>
       <c r="E36" t="n">
-        <v>279</v>
+        <v>140</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-e9aa6b4a93", "line_id": "L-39c61f25c8", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2742,7 @@
         <v>-14</v>
       </c>
       <c r="E37" t="n">
-        <v>265</v>
+        <v>126</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2706,23 +2761,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-14</v>
+        <v>147</v>
       </c>
       <c r="E38" t="n">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>receivable_collected | {"receivable_id": "AR-1069f828ac"}</t>
         </is>
       </c>
     </row>
@@ -2739,11 +2794,11 @@
         <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2758,14 +2813,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>222</v>
+        <v>259</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2774,7 +2829,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-39c61f25c8"}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-4-0022", "receivable_term_quarters": 4, "revenue_wan": 42.0}</t>
         </is>
       </c>
     </row>
@@ -2784,14 +2839,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E41" t="n">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2800,7 +2855,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-39c61f25c8", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2810,14 +2865,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E42" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2826,7 +2881,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-39c61f25c8", "asset_type": "production_line"}</t>
+          <t>maintenance_expense | {"line_id": "L-39c61f25c8"}</t>
         </is>
       </c>
     </row>
@@ -2836,23 +2891,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-39c61f25c8", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2862,23 +2917,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-39c61f25c8", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2888,23 +2943,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E45" t="n">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2921,11 +2976,11 @@
         <v>-14</v>
       </c>
       <c r="E46" t="n">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2940,23 +2995,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E47" t="n">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-39c61f25c8"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2966,23 +3021,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E48" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-39c61f25c8", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2992,21 +3047,99 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>Update_Receivable</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>42</v>
+      </c>
+      <c r="E49" t="n">
+        <v>218</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>第5年3季</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>receivable_collected | {"receivable_id": "AR-77aff7f27a"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>47</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Pay_Maintenance</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>-15</v>
+      </c>
+      <c r="E50" t="n">
+        <v>203</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>maintenance_expense | {"line_id": "L-39c61f25c8"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>48</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>157</v>
-      </c>
-      <c r="F49" t="inlineStr">
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>203</v>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>第5年4季</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-39c61f25c8", "asset_type": "factory"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>49</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>203</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-39c61f25c8", "asset_type": "production_line"}</t>
         </is>
@@ -3113,16 +3246,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3338,16 +3471,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H13" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -3403,10 +3536,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="G16" t="n">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3428,10 +3561,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3453,10 +3586,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G18" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3475,16 +3608,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H19" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -3500,16 +3633,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-79</v>
+        <v>-83</v>
       </c>
       <c r="F20" t="n">
-        <v>-79</v>
+        <v>-16</v>
       </c>
       <c r="G20" t="n">
-        <v>-52</v>
+        <v>-61</v>
       </c>
       <c r="H20" t="n">
-        <v>-65</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="21">
@@ -3550,16 +3683,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-94.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-94.2</v>
+        <v>-31.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-67.2</v>
+        <v>-76.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-80.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="23">
@@ -3600,16 +3733,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-94.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-94.2</v>
+        <v>-31.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-67.2</v>
+        <v>-76.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-80.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="25">
@@ -3650,16 +3783,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-94.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-94.2</v>
+        <v>-31.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-67.2</v>
+        <v>-76.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-80.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="28">
@@ -3749,16 +3882,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F30" t="n">
-        <v>274</v>
+        <v>166</v>
       </c>
       <c r="G30" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="H30" t="n">
-        <v>157</v>
+        <v>203</v>
       </c>
     </row>
     <row r="31">
@@ -3777,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -3802,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -3827,7 +3960,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -3874,16 +4007,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F35" t="n">
-        <v>334</v>
+        <v>393</v>
       </c>
       <c r="G35" t="n">
-        <v>282</v>
+        <v>332</v>
       </c>
       <c r="H35" t="n">
-        <v>217</v>
+        <v>263</v>
       </c>
     </row>
     <row r="36">
@@ -3999,16 +4132,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>494.6</v>
+        <v>490.6</v>
       </c>
       <c r="F40" t="n">
-        <v>400.4</v>
+        <v>459.4</v>
       </c>
       <c r="G40" t="n">
-        <v>333.2</v>
+        <v>383.2</v>
       </c>
       <c r="H40" t="n">
-        <v>253</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41">
@@ -4177,13 +4310,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-180.4</v>
+        <v>-184.4000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>-274.6</v>
+        <v>-215.6000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>-341.8</v>
+        <v>-291.8000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -4199,16 +4332,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-94.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-94.2</v>
+        <v>-31.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-67.2</v>
+        <v>-76.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-80.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="49">
@@ -4224,16 +4357,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>494.6</v>
+        <v>490.6</v>
       </c>
       <c r="F49" t="n">
-        <v>400.4</v>
+        <v>459.3999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>333.2</v>
+        <v>383.1999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>253</v>
+        <v>298.9999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4249,16 +4382,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>494.6</v>
+        <v>490.6</v>
       </c>
       <c r="F50" t="n">
-        <v>400.4</v>
+        <v>459.3999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>333.2</v>
+        <v>383.1999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>253</v>
+        <v>298.9999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4329,7 +4462,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4478,7 +4611,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4627,7 +4760,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4776,7 +4909,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -4925,7 +5058,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
